--- a/static/data/exports/Retro_JK_AE_2014.xlsx
+++ b/static/data/exports/Retro_JK_AE_2014.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/static/data/exports/Retro_JK_AE_2014.xlsx
+++ b/static/data/exports/Retro_JK_AE_2014.xlsx
@@ -23232,11 +23232,11 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D368" t="n">
-        <v>24876</v>
+        <v>24857</v>
       </c>
       <c r="E368" t="n">
         <v>2779</v>
@@ -25464,11 +25464,11 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D404" t="n">
-        <v>24876</v>
+        <v>24857</v>
       </c>
       <c r="E404" t="n">
         <v>20574</v>
@@ -36624,11 +36624,11 @@
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D584" t="n">
-        <v>24876</v>
+        <v>24857</v>
       </c>
       <c r="E584" t="n">
         <v>664</v>
@@ -54409,11 +54409,11 @@
     </row>
     <row r="871">
       <c r="A871" t="n">
-        <v>1933761</v>
+        <v>1933760</v>
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>Ghulam Mustafa</t>
+          <t>Istkhar Ali Ahmed</t>
         </is>
       </c>
       <c r="C871" t="inlineStr">
@@ -54446,7 +54446,7 @@
       </c>
       <c r="K871" t="inlineStr">
         <is>
-          <t>Ghulam Mustafa</t>
+          <t>Istkhar Ali Ahmed</t>
         </is>
       </c>
       <c r="L871" t="inlineStr">
@@ -54471,11 +54471,11 @@
     </row>
     <row r="872">
       <c r="A872" t="n">
-        <v>1933760</v>
+        <v>1933761</v>
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>Istkhar Ali Ahmed</t>
+          <t>Ghulam Mustafa</t>
         </is>
       </c>
       <c r="C872" t="inlineStr">
@@ -54508,7 +54508,7 @@
       </c>
       <c r="K872" t="inlineStr">
         <is>
-          <t>Istkhar Ali Ahmed</t>
+          <t>Ghulam Mustafa</t>
         </is>
       </c>
       <c r="L872" t="inlineStr">
